--- a/Rela_televendas.xlsx
+++ b/Rela_televendas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eder\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE47371-F712-4BB6-A855-2DFB42A86A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F24FC33-ED43-4C99-9881-A2887D66F4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A89541A1-984B-48A7-B04B-EE0D6FC9B806}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A89541A1-984B-48A7-B04B-EE0D6FC9B806}"/>
   </bookViews>
   <sheets>
     <sheet name="quantidade por horário" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="65">
   <si>
     <t>Seg</t>
   </si>
@@ -182,9 +182,6 @@
   </si>
   <si>
     <t>Francinele</t>
-  </si>
-  <si>
-    <t>VENDODORA</t>
   </si>
   <si>
     <t>R$ VENDAS</t>
@@ -287,14 +284,14 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -713,7 +710,7 @@
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>45962</v>
       </c>
       <c r="B2" t="s">
@@ -793,7 +790,7 @@
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
+      <c r="A3" s="7"/>
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -871,7 +868,7 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
+      <c r="A4" s="7"/>
       <c r="B4" t="s">
         <v>2</v>
       </c>
@@ -949,7 +946,7 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
+      <c r="A5" s="7"/>
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -1027,7 +1024,7 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
+      <c r="A6" s="7"/>
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -1105,7 +1102,7 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
+      <c r="A7" s="7"/>
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -1183,7 +1180,7 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
+      <c r="A8" s="7"/>
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -1261,7 +1258,7 @@
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
+      <c r="A9" s="7"/>
       <c r="C9" t="s">
         <v>7</v>
       </c>
@@ -1339,7 +1336,7 @@
       <c r="A10" s="4"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11" s="7">
         <v>45992</v>
       </c>
       <c r="B11" t="s">
@@ -1419,7 +1416,7 @@
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
+      <c r="A12" s="7"/>
       <c r="B12" t="s">
         <v>0</v>
       </c>
@@ -1497,7 +1494,7 @@
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
+      <c r="A13" s="7"/>
       <c r="B13" t="s">
         <v>1</v>
       </c>
@@ -1575,7 +1572,7 @@
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
+      <c r="A14" s="7"/>
       <c r="B14" t="s">
         <v>2</v>
       </c>
@@ -1653,7 +1650,7 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
+      <c r="A15" s="7"/>
       <c r="B15" t="s">
         <v>3</v>
       </c>
@@ -1731,7 +1728,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
+      <c r="A16" s="7"/>
       <c r="B16" t="s">
         <v>4</v>
       </c>
@@ -1809,7 +1806,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
+      <c r="A17" s="7"/>
       <c r="B17" t="s">
         <v>5</v>
       </c>
@@ -1887,7 +1884,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
+      <c r="A18" s="7"/>
       <c r="B18" t="s">
         <v>6</v>
       </c>
@@ -1965,7 +1962,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
+      <c r="A19" s="7"/>
       <c r="C19" t="s">
         <v>7</v>
       </c>
@@ -2121,7 +2118,7 @@
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
+      <c r="A22" s="7">
         <v>46023</v>
       </c>
       <c r="B22" t="s">
@@ -2201,7 +2198,7 @@
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
+      <c r="A23" s="7"/>
       <c r="B23" t="s">
         <v>1</v>
       </c>
@@ -2279,7 +2276,7 @@
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
+      <c r="A24" s="7"/>
       <c r="B24" t="s">
         <v>2</v>
       </c>
@@ -2357,7 +2354,7 @@
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
+      <c r="A25" s="7"/>
       <c r="B25" t="s">
         <v>3</v>
       </c>
@@ -2435,7 +2432,7 @@
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
+      <c r="A26" s="7"/>
       <c r="B26" t="s">
         <v>4</v>
       </c>
@@ -2513,7 +2510,7 @@
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
+      <c r="A27" s="7"/>
       <c r="B27" t="s">
         <v>5</v>
       </c>
@@ -2591,7 +2588,7 @@
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
+      <c r="A28" s="7"/>
       <c r="B28" t="s">
         <v>6</v>
       </c>
@@ -2669,7 +2666,7 @@
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
+      <c r="A29" s="7"/>
       <c r="C29" t="s">
         <v>7</v>
       </c>
@@ -2822,7 +2819,7 @@
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
+      <c r="A31" s="7">
         <v>46054</v>
       </c>
       <c r="B31" t="s">
@@ -2902,7 +2899,7 @@
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
+      <c r="A32" s="7"/>
       <c r="B32" t="s">
         <v>1</v>
       </c>
@@ -2980,7 +2977,7 @@
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
+      <c r="A33" s="7"/>
       <c r="B33" t="s">
         <v>2</v>
       </c>
@@ -3058,7 +3055,7 @@
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
+      <c r="A34" s="7"/>
       <c r="B34" t="s">
         <v>3</v>
       </c>
@@ -3136,7 +3133,7 @@
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
+      <c r="A35" s="7"/>
       <c r="B35" t="s">
         <v>4</v>
       </c>
@@ -3214,7 +3211,7 @@
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
+      <c r="A36" s="7"/>
       <c r="B36" t="s">
         <v>5</v>
       </c>
@@ -3292,7 +3289,7 @@
       </c>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
+      <c r="A37" s="7"/>
       <c r="B37" t="s">
         <v>6</v>
       </c>
@@ -3370,7 +3367,7 @@
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
+      <c r="A38" s="7"/>
       <c r="B38" t="s">
         <v>32</v>
       </c>
@@ -3451,7 +3448,7 @@
       <c r="A39" s="4"/>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
+      <c r="A40" s="7">
         <v>46082</v>
       </c>
       <c r="B40" t="s">
@@ -3531,7 +3528,7 @@
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
+      <c r="A41" s="7"/>
       <c r="B41" t="s">
         <v>0</v>
       </c>
@@ -3609,7 +3606,7 @@
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
+      <c r="A42" s="7"/>
       <c r="B42" t="s">
         <v>1</v>
       </c>
@@ -3687,7 +3684,7 @@
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
+      <c r="A43" s="7"/>
       <c r="B43" t="s">
         <v>2</v>
       </c>
@@ -3765,7 +3762,7 @@
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
+      <c r="A44" s="7"/>
       <c r="B44" t="s">
         <v>3</v>
       </c>
@@ -3843,7 +3840,7 @@
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
+      <c r="A45" s="7"/>
       <c r="B45" t="s">
         <v>4</v>
       </c>
@@ -3921,7 +3918,7 @@
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A46" s="5"/>
+      <c r="A46" s="7"/>
       <c r="B46" t="s">
         <v>5</v>
       </c>
@@ -3999,7 +3996,7 @@
       </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A47" s="5"/>
+      <c r="A47" s="7"/>
       <c r="B47" t="s">
         <v>6</v>
       </c>
@@ -4077,7 +4074,7 @@
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
+      <c r="A48" s="7"/>
       <c r="C48" t="s">
         <v>7</v>
       </c>
@@ -4155,7 +4152,7 @@
       <c r="A49" s="4"/>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A50" s="5">
+      <c r="A50" s="7">
         <v>46113</v>
       </c>
       <c r="B50" t="s">
@@ -4235,7 +4232,7 @@
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A51" s="5"/>
+      <c r="A51" s="7"/>
       <c r="B51" t="s">
         <v>0</v>
       </c>
@@ -4313,7 +4310,7 @@
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A52" s="5"/>
+      <c r="A52" s="7"/>
       <c r="B52" t="s">
         <v>1</v>
       </c>
@@ -4391,7 +4388,7 @@
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A53" s="5"/>
+      <c r="A53" s="7"/>
       <c r="B53" t="s">
         <v>2</v>
       </c>
@@ -4469,7 +4466,7 @@
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A54" s="5"/>
+      <c r="A54" s="7"/>
       <c r="B54" t="s">
         <v>3</v>
       </c>
@@ -4547,7 +4544,7 @@
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A55" s="5"/>
+      <c r="A55" s="7"/>
       <c r="B55" t="s">
         <v>4</v>
       </c>
@@ -4625,7 +4622,7 @@
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A56" s="5"/>
+      <c r="A56" s="7"/>
       <c r="B56" t="s">
         <v>5</v>
       </c>
@@ -4703,7 +4700,7 @@
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A57" s="5"/>
+      <c r="A57" s="7"/>
       <c r="B57" t="s">
         <v>6</v>
       </c>
@@ -4781,7 +4778,7 @@
       </c>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A58" s="5"/>
+      <c r="A58" s="7"/>
       <c r="C58" t="s">
         <v>7</v>
       </c>
@@ -4883,7 +4880,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
         <v>34</v>
@@ -4905,16 +4902,16 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>45962</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>288</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="6">
         <v>2900</v>
       </c>
       <c r="E2" s="1">
@@ -4924,18 +4921,18 @@
         <v>1.0069444444444444E-3</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
+      <c r="A3" s="7"/>
       <c r="B3" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>212</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>1800</v>
       </c>
       <c r="E3" s="1">
@@ -4945,27 +4942,27 @@
         <v>1.0300925925925926E-3</v>
       </c>
       <c r="G3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="7">
         <v>45992</v>
       </c>
       <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>334</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>3200</v>
       </c>
       <c r="E5" s="1">
@@ -4975,18 +4972,18 @@
         <v>1.2731481481481483E-3</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
+      <c r="A6" s="7"/>
       <c r="B6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>216</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>1500</v>
       </c>
       <c r="E6" s="1">
@@ -4996,27 +4993,27 @@
         <v>9.1435185185185185E-4</v>
       </c>
       <c r="G6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="7">
         <v>46023</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>217</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>2400</v>
       </c>
       <c r="E8" s="1">
@@ -5026,18 +5023,18 @@
         <v>8.3333333333333339E-4</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
+      <c r="A9" s="7"/>
       <c r="B9" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>131</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>1100</v>
       </c>
       <c r="E9" s="1">
@@ -5047,27 +5044,27 @@
         <v>8.4490740740740739E-4</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11" s="7">
         <v>46054</v>
       </c>
       <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
         <v>0</v>
       </c>
       <c r="E11" s="1">
@@ -5081,14 +5078,14 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
+      <c r="A12" s="7"/>
       <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="6">
         <v>377</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <v>2400</v>
       </c>
       <c r="E12" s="1">
@@ -5103,22 +5100,22 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+      <c r="A14" s="7">
         <v>46082</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>283</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>2500</v>
       </c>
       <c r="E14" s="1">
@@ -5128,18 +5125,18 @@
         <v>9.3749999999999997E-4</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
+      <c r="A15" s="7"/>
       <c r="B15" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="6">
         <v>111</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <v>880</v>
       </c>
       <c r="E15" s="1">
@@ -5154,22 +5151,22 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
+      <c r="A17" s="7">
         <v>46113</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="6">
         <v>223</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>2100</v>
       </c>
       <c r="E17" s="1">
@@ -5179,18 +5176,18 @@
         <v>9.2592592592592596E-4</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
+      <c r="A18" s="7"/>
       <c r="B18" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="6">
         <v>139</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="6">
         <v>976</v>
       </c>
       <c r="E18" s="1">
@@ -5231,29 +5228,29 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
         <v>47</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
         <v>48</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" t="s">
-        <v>52</v>
-      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="7">
         <v>45962</v>
       </c>
       <c r="B2" t="s">
@@ -5262,40 +5259,40 @@
       <c r="C2" s="2">
         <v>310768.77</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <v>172</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="5">
         <v>138</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="F2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="8">
         <v>410000</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
+      <c r="A3" s="7"/>
       <c r="B3" t="s">
         <v>46</v>
       </c>
       <c r="C3" s="2">
         <v>269293.15000000002</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>146</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>126</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="6"/>
+      <c r="F3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="8"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="7">
         <v>45992</v>
       </c>
       <c r="B4" t="s">
@@ -5304,40 +5301,40 @@
       <c r="C4" s="2">
         <v>227420.75</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>132</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>94</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="F4" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="8">
         <v>490000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
+      <c r="A5" s="7"/>
       <c r="B5" t="s">
         <v>46</v>
       </c>
       <c r="C5" s="2">
         <v>186079.55</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>90</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>78</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="6"/>
+      <c r="F5" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="7">
         <v>46023</v>
       </c>
       <c r="B6" t="s">
@@ -5346,40 +5343,40 @@
       <c r="C6" s="2">
         <v>183313.34</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>101</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>79</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="F6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="8">
         <v>400000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
+      <c r="A7" s="7"/>
       <c r="B7" t="s">
         <v>46</v>
       </c>
       <c r="C7" s="2">
         <v>137782.74</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>74</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>62</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="6"/>
+      <c r="F7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="7">
         <v>46054</v>
       </c>
       <c r="B8" t="s">
@@ -5388,40 +5385,40 @@
       <c r="C8" s="2">
         <v>0</v>
       </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="8">
         <v>550000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
+      <c r="A9" s="7"/>
       <c r="B9" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="2">
         <v>279398</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>155</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <v>109</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="6"/>
+      <c r="F9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="A10" s="7">
         <v>46082</v>
       </c>
       <c r="B10" t="s">
@@ -5430,40 +5427,40 @@
       <c r="C10" s="2">
         <v>165800.85</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>85</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>71</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="F10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="8">
         <v>360000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
+      <c r="A11" s="7"/>
       <c r="B11" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="2">
         <v>117160.44</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>59</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="5">
         <v>51</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="6"/>
+      <c r="F11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="8"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="A12" s="7">
         <v>46113</v>
       </c>
       <c r="B12" t="s">
@@ -5472,37 +5469,37 @@
       <c r="C12" s="2">
         <v>207544.93</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>95</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="5">
         <v>98</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="F12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="8">
         <v>300000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
+      <c r="A13" s="7"/>
       <c r="B13" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="2">
         <v>162609.04999999999</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>78</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="5">
         <v>66</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="F14" s="3"/>
